--- a/SSTSS_GenSim_Modules/Scenario_Selection_Module/user_selected_ODD.xlsx
+++ b/SSTSS_GenSim_Modules/Scenario_Selection_Module/user_selected_ODD.xlsx
@@ -903,31 +903,31 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>

--- a/SSTSS_GenSim_Modules/Scenario_Selection_Module/user_selected_ODD.xlsx
+++ b/SSTSS_GenSim_Modules/Scenario_Selection_Module/user_selected_ODD.xlsx
@@ -924,10 +924,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
